--- a/output/roomself_excel/4674.xlsx
+++ b/output/roomself_excel/4674.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3432</v>
       </c>
-      <c r="E2" t="n">
-        <v>478</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>432</v>
+        <v>406</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>447</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>1732</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>221</v>
       </c>
-      <c r="F3" t="n">
-        <v>26</v>
-      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2948</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>363</v>
       </c>
-      <c r="F4" t="n">
-        <v>26</v>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>374</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>3020</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +631,27 @@
       <c r="D6" t="n">
         <v>2940</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>372</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>305</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -585,10 +669,26 @@
       <c r="D7" t="n">
         <v>2800</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>294</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>406</v>
+      </c>
+      <c r="J7" t="n">
         <v>26</v>
       </c>
     </row>
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>1044</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
